--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AO8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1525,7 +1525,221 @@
           <t>Edwin radica</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6a2890f1a0cc341db</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:15:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>calle sur envigado</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>barrio 1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>andres@gmail.com</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Queja / reporte ambiental</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Fauna doméstica</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>restaurante el puerquito</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>calle 1</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>barrio 1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>maltratan perritos callejeros</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>respuesta</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6a288dd6df5510af0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:02:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ENV-FLO-1-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jorge Iván Montoya</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>80123456</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cl 38 Sur # 42-05</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3156677889</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>barrio 2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>jorge.montoya@email.com</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Sugerencia</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1034567890</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3182233445</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Cl 39 Sur # 41-20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>barrio 1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Propuesta de siembra de árboles nativos en zona verde del barrio afectada por tala informal.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro CRM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,12 +25,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00444444"/>
+      <color rgb="FF444444"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -43,12 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E7D32"/>
+        <fgColor rgb="FF2E7D32"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +82,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -440,50 +445,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AO7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15.3" customWidth="1" min="3" max="3"/>
-    <col width="27.2" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="19.55" customWidth="1" min="6" max="6"/>
-    <col width="22.1" customWidth="1" min="7" max="7"/>
-    <col width="21.25" customWidth="1" min="8" max="8"/>
-    <col width="19.55" customWidth="1" min="9" max="9"/>
-    <col width="15.3" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="1" max="2"/>
+    <col width="15.33203125" customWidth="1" min="3" max="3"/>
+    <col width="27.1640625" customWidth="1" min="4" max="4"/>
+    <col width="23.83203125" customWidth="1" min="5" max="5"/>
+    <col width="19.5" customWidth="1" min="6" max="6"/>
+    <col width="22.1640625" customWidth="1" min="7" max="7"/>
+    <col width="21.1640625" customWidth="1" min="8" max="8"/>
+    <col width="19.5" customWidth="1" min="9" max="9"/>
+    <col width="15.33203125" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14.45" customWidth="1" min="12" max="12"/>
-    <col width="16.15" customWidth="1" min="13" max="13"/>
-    <col width="27.2" customWidth="1" min="14" max="14"/>
-    <col width="21.25" customWidth="1" min="15" max="15"/>
-    <col width="22.1" customWidth="1" min="16" max="16"/>
-    <col width="19.55" customWidth="1" min="17" max="17"/>
+    <col width="14.5" customWidth="1" min="12" max="12"/>
+    <col width="16.1640625" customWidth="1" min="13" max="13"/>
+    <col width="27.1640625" customWidth="1" min="14" max="14"/>
+    <col width="21.1640625" customWidth="1" min="15" max="15"/>
+    <col width="22.1640625" customWidth="1" min="16" max="16"/>
+    <col width="19.5" customWidth="1" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="16.15" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="19.55" customWidth="1" min="22" max="22"/>
-    <col width="15.3" customWidth="1" min="23" max="23"/>
+    <col width="16.1640625" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="21"/>
+    <col width="19.5" customWidth="1" min="22" max="22"/>
+    <col width="15.33203125" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="24.65" customWidth="1" min="25" max="25"/>
-    <col width="14.45" customWidth="1" min="26" max="26"/>
+    <col width="24.6640625" customWidth="1" min="25" max="25"/>
+    <col width="14.5" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="16.15" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="28" max="30"/>
+    <col width="16.1640625" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="20.4" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="15.3" customWidth="1" min="36" max="36"/>
+    <col width="20.33203125" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="35"/>
+    <col width="15.33203125" customWidth="1" min="36" max="36"/>
     <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14.45" customWidth="1" min="38" max="38"/>
-    <col width="18.7" customWidth="1" min="39" max="39"/>
+    <col width="14.5" customWidth="1" min="38" max="38"/>
+    <col width="18.6640625" customWidth="1" min="39" max="39"/>
     <col width="17" customWidth="1" min="40" max="40"/>
-    <col width="17.85" customWidth="1" min="41" max="41"/>
+    <col width="17.83203125" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ENV-RSO-1-2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-2</t>
+          <t>2026-1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1422,42 +1422,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6a288a85cdaa7b61e</t>
+          <t>6a2890f1a0cc341db</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:48:00</t>
+          <t>2026-06-07 21:00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-3</t>
+          <t>2026-6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ana Lucía Gómez</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52987643</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cra 50 # 30-22 Apto 401</t>
+          <t>calle sur envigado</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3205544332</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ana.gomez@email.com</t>
+          <t>andres@gmail.com</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1477,37 +1477,37 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PQRSD</t>
+          <t>Queja / reporte ambiental</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hídrico</t>
+          <t>Fauna doméstica</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Industrias del Valle Ltda. NIT perjudicante</t>
+          <t>restaurante el puerquito</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>6045559012</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Zona industrial La Tablaza Bodega 14</t>
+          <t>calle 1</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>barrio 2</t>
+          <t>barrio 1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Agua con olor y coloración en quebrada cercana a planta industrial.</t>
+          <t>maltratan perritos callejeros</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1529,97 +1529,97 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6a2890f1a0cc341db</t>
+          <t>6a288dd6df5510af0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-09 22:15:00</t>
+          <t>2026-06-09 22:02:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>ENV-FLO-1-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-6</t>
+          <t>2026-1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Jorge Iván Montoya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>80123456</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>calle sur envigado</t>
+          <t>Cl 38 Sur # 42-05</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>3156677889</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>barrio 2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>jorge.montoya@email.com</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Sugerencia</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1034567890</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3182233445</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Cl 39 Sur # 41-20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>barrio 1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>andres@gmail.com</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Queja / reporte ambiental</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Fauna doméstica</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>restaurante el puerquito</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>calle 1</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>barrio 1</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>maltratan perritos callejeros</t>
+          <t>Propuesta de siembra de árboles nativos en zona verde del barrio afectada por tala informal.</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>respuesta</t>
+          <t>Respuesta</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1632,114 +1632,6 @@
           <t>Edwin radica</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6a288dd6df5510af0</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-09 22:02:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ENV-FLO-1-2026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Jorge Iván Montoya</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>80123456</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Cl 38 Sur # 42-05</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3156677889</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>barrio 2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>jorge.montoya@email.com</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Telefono</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Sugerencia</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1034567890</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>3182233445</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Cl 39 Sur # 41-20</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>barrio 1</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Propuesta de siembra de árboles nativos en zona verde del barrio afectada por tala informal.</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Juan Carlos Sanchez</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Edwin radica</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro CRM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -25,18 +26,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <i val="1"/>
-      <color rgb="FF444444"/>
-      <sz val="11"/>
+      <color rgb="00444444"/>
     </font>
   </fonts>
   <fills count="4">
@@ -48,12 +43,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E7D32"/>
+        <fgColor rgb="002E7D32"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -80,9 +75,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -445,45 +442,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:AV4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="2"/>
-    <col width="15.33203125" customWidth="1" min="3" max="3"/>
-    <col width="27.1640625" customWidth="1" min="4" max="4"/>
-    <col width="23.83203125" customWidth="1" min="5" max="5"/>
-    <col width="19.5" customWidth="1" min="6" max="6"/>
-    <col width="22.1640625" customWidth="1" min="7" max="7"/>
-    <col width="21.1640625" customWidth="1" min="8" max="8"/>
-    <col width="19.5" customWidth="1" min="9" max="9"/>
-    <col width="15.33203125" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15.3" customWidth="1" min="3" max="3"/>
+    <col width="27.2" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="19.55" customWidth="1" min="6" max="6"/>
+    <col width="22.1" customWidth="1" min="7" max="7"/>
+    <col width="21.25" customWidth="1" min="8" max="8"/>
+    <col width="19.55" customWidth="1" min="9" max="9"/>
+    <col width="15.3" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14.5" customWidth="1" min="12" max="12"/>
-    <col width="16.1640625" customWidth="1" min="13" max="13"/>
-    <col width="27.1640625" customWidth="1" min="14" max="14"/>
-    <col width="21.1640625" customWidth="1" min="15" max="15"/>
-    <col width="22.1640625" customWidth="1" min="16" max="16"/>
-    <col width="19.5" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="16.1640625" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="21"/>
-    <col width="19.5" customWidth="1" min="22" max="22"/>
-    <col width="15.33203125" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="24.6640625" customWidth="1" min="25" max="25"/>
-    <col width="14.5" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="30"/>
-    <col width="16.1640625" customWidth="1" min="31" max="31"/>
-    <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="20.33203125" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="35"/>
-    <col width="15.33203125" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14.5" customWidth="1" min="38" max="38"/>
-    <col width="18.6640625" customWidth="1" min="39" max="39"/>
-    <col width="17" customWidth="1" min="40" max="40"/>
-    <col width="17.83203125" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="16.15" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14.45" customWidth="1" min="18" max="18"/>
+    <col width="27.2" customWidth="1" min="19" max="19"/>
+    <col width="22.1" customWidth="1" min="20" max="20"/>
+    <col width="21.25" customWidth="1" min="21" max="21"/>
+    <col width="22.1" customWidth="1" min="22" max="22"/>
+    <col width="19.55" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="24" max="24"/>
+    <col width="16.15" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="19.55" customWidth="1" min="28" max="28"/>
+    <col width="15.3" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="24.65" customWidth="1" min="31" max="31"/>
+    <col width="14.45" customWidth="1" min="32" max="32"/>
+    <col width="17" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="16.15" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="20.4" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="14" customWidth="1" min="41" max="41"/>
+    <col width="15.3" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="14.45" customWidth="1" min="44" max="44"/>
+    <col width="18.7" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="46" max="46"/>
+    <col width="17.85" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -544,152 +553,187 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de solicitud</t>
+          <t>Recurso / tema</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Asunto</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Categoría ambiental</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de vencimiento</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Última actuación</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Próxima actuación</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Perjudicante / posible afectante</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Documento del perjudicante</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Teléfono del perjudicante</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Dirección del perjudicante</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Barrio del perjudicante</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Descripción de la queja / reporte</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Respuesta inmediata</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Recibida por</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Remitido a</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Asignado a (patrullero)</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>Fecha de la visita</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Año acta</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>Autorización datos personales</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>Posible afectante</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>Dirección afectación</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>Teléfono (acta)</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AI1" s="2" t="inlineStr">
         <is>
           <t>Barrio (acta)</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AJ1" s="2" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AK1" s="2" t="inlineStr">
         <is>
           <t>Objeto de la visita</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AL1" s="2" t="inlineStr">
         <is>
           <t>Situación encontrada</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AM1" s="2" t="inlineStr">
         <is>
           <t>Análisis de la situación</t>
         </is>
       </c>
-      <c r="AH1" s="2" t="inlineStr">
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>Conclusión</t>
         </is>
       </c>
-      <c r="AI1" s="2" t="inlineStr">
+      <c r="AO1" s="2" t="inlineStr">
         <is>
           <t>Requerimientos</t>
         </is>
       </c>
-      <c r="AJ1" s="2" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>Nombre funcionario</t>
         </is>
       </c>
-      <c r="AK1" s="2" t="inlineStr">
+      <c r="AQ1" s="2" t="inlineStr">
         <is>
           <t>C.C. funcionario</t>
         </is>
       </c>
-      <c r="AL1" s="2" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>Cargo funcionario</t>
         </is>
       </c>
-      <c r="AM1" s="2" t="inlineStr">
+      <c r="AS1" s="2" t="inlineStr">
         <is>
           <t>Nombre establecimiento</t>
         </is>
       </c>
-      <c r="AN1" s="2" t="inlineStr">
+      <c r="AT1" s="2" t="inlineStr">
         <is>
           <t>C.C. establecimiento</t>
         </is>
       </c>
-      <c r="AO1" s="2" t="inlineStr">
+      <c r="AU1" s="2" t="inlineStr">
         <is>
           <t>Cargo establecimiento</t>
+        </is>
+      </c>
+      <c r="AV1" s="4" t="inlineStr">
+        <is>
+          <t>Fecha del acta</t>
         </is>
       </c>
     </row>
@@ -751,169 +795,204 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>cTipo</t>
+          <t>cRecursoTema</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
+          <t>cAsunto</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>cZonaAlcaldia</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
           <t>cCategoria</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>cFechaVencimiento</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>cUltimaActuacion</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>cProximaActuacion</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>cPerjudicante</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>cDocumentoPerjudicante</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>cTelefonoPerjudicante</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>cDireccionPerjudicante</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>cBarrioPerjudicante</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>cRespuestaInmediata</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>cRecibidaPor</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>cRemitidoA</t>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>assignedUser</t>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>fechaVisita</t>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>autorizacionDatos</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <t>posibleAfectante</t>
         </is>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <t>direccionAfectacion</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AH2" s="3" t="inlineStr">
         <is>
           <t>telefono</t>
         </is>
       </c>
-      <c r="AC2" s="3" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <t>barrio</t>
         </is>
       </c>
-      <c r="AD2" s="3" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <t>zona</t>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr">
         <is>
           <t>objetoVisita</t>
         </is>
       </c>
-      <c r="AF2" s="3" t="inlineStr">
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <t>situacionEncontrada</t>
         </is>
       </c>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <t>analisisSituacion</t>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
+      <c r="AN2" s="3" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
       </c>
-      <c r="AI2" s="3" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>requerimientos</t>
         </is>
       </c>
-      <c r="AJ2" s="3" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <t>funcionarioNombre</t>
         </is>
       </c>
-      <c r="AK2" s="3" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
         <is>
           <t>funcionarioCedula</t>
         </is>
       </c>
-      <c r="AL2" s="3" t="inlineStr">
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <t>funcionarioCargo</t>
         </is>
       </c>
-      <c r="AM2" s="3" t="inlineStr">
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <t>establecimientoNombre</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <t>establecimientoCedula</t>
         </is>
       </c>
-      <c r="AO2" s="3" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <t>establecimientoCargo</t>
+        </is>
+      </c>
+      <c r="AV2" s="5" t="inlineStr">
+        <is>
+          <t>fecha</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6a2884b9de30c433b</t>
+          <t>6a2a0f36a3b72befb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-09 21:23:00</t>
+          <t>2026-06-11 01:19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ENV-AIR-1-2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -928,27 +1007,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43219876</t>
+          <t>1011390467</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cra 48 # 32-10</t>
+          <t>calle 23 #40-09</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3001112233</t>
+          <t>3052661092</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>barrio 1</t>
+          <t>Alto de Misael</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>maria.restrepo@email.com</t>
+          <t>MarieElena@gmail.com</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -958,207 +1037,239 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Queja / reporte ambiental</t>
+          <t>AIRE</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Aire</t>
+          <t>Control socioambiental de obra</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>maria.restrepo@email.com</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3001112233</t>
+          <t>Suelo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Cra 48 # 32-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>barrio 1</t>
+          <t>Remisión</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Ruido excesivo por obra en horario nocturno frente a la vivienda.</t>
+          <t>Verificación</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>respuesta</t>
+          <t>Constructora SAS</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>3-5697</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>30256914</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>constructora@gmail.com</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Alto de Misael</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>Juan Carlos Sanchez</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Edwin radica</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>patrullero 1</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>maria.restrepo@email.com</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Cra 48 # 32-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>3001112233</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>barrio 1</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Constructora SAS</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>calle 23 #40-09</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>3052661092</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Alto de Misael</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Urbano</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Verificar queja por ruido excesivo proveniente de obra de construcción en horario nocturno, que afecta la vivienda de la peticionaria en Cra 48 # 32-10, conforme a la solicitud radicada por María Elena Restrepo.</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>En la visita se constató obra de construcción en lote contiguo a la vivienda de la peticionaria. Se evidenció uso de herramienta eléctrica (taladro y cortadora) después de las 8:00 p.m. La peticionaria manifestó que el ruido se presenta de forma reiterada entre 8:00 p.m. y 10:30 p.m., afectando el descanso de su núcleo familiar. No se observó cartel de horarios de trabajo ni medidas de mitigación de ruido en el frente de obra.</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>La actividad reportada corresponde a fuente de ruido de carácter intermitente en zona urbana residencial. El horario reportado coincide con periodos de mayor sensibilidad acústica según normativa municipal. Se requiere verificar permisos de construcción y horarios autorizados para labores ruidosas. La afectación se considera plausible según lo manifestado y lo observado en sitio.</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Se confirma presencia de obra activa en predio colindante al lugar de la queja. Existe indicio de emisión de ruido en horario nocturno. Se recomienda solicitar al responsable de la obra la suspensión de actividades ruidosas fuera del horario permitido y el cumplimiento de medidas de control de ruido.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1. Presentar permiso de construcción y horarios autorizados de trabajo.
-2. Cesar actividades ruidosas fuera del horario diurno permitido.
-3. Implementar barreras o medidas de mitigación de ruido en el frente de obra.
-4. Remitir plan de manejo de ruido si la actividad continúa por más de 15 días.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>objetivo visita</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>situacion encontrada</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>analisis de la situacion</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>conclusion</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>requerimientos</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>patrullero 1</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>1012345678</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Patrullero ambientall</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>María Elena Restrepo</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>43219876</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Peticionaria / Propietaria del inmueble</t>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>12456</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>patrullero</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>establecimiento</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>128933</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>cargo</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6a2888f6d6af12923</t>
+          <t>6a2a17df3292bdb12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09 21:41:00</t>
+          <t>2026-06-11 02:03:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ENV-RSO-1-2026</t>
+          <t>ENV-AIR-2-2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-1</t>
+          <t>2026-2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Constructora El Mirador S.A.S.</t>
+          <t>Carlos Torres</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>900123456-7</t>
+          <t>985641</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cl 37 Sur # 28-50 Of. 302</t>
+          <t>carrera 23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6043218877</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>barrio 1</t>
+          <t>El Chingui</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mailto:ambiental@elmirador.com</t>
+          <t>carlos@gmail.com</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1168,470 +1279,76 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Denuncia</t>
+          <t>AIRE</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Residuos sólidos</t>
+          <t>Afectaciones por ruido</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Carlos Andrés Mejía</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>3109987766</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Cl 35 Sur # 26-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>barrio 1</t>
+          <t>Remisión</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Vertimiento irregular de escombros en vía pública desde obra de la constructora.</t>
+          <t>Verificación</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Respuesta</t>
+          <t>lula martinez</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>lula martinez</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>El Chingui</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>respuesta</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>Juan Carlos Sanchez</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Edwin radica</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>patrullero 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6a288b63e1d1e2bce</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-09 21:51:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Parque Logístico Envigado S.A.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>901234567-8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Autopista Sur Km 14 Bodega 8</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>6047778899</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>barrio 2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>operaciones@parquelogistico.com</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Telefono</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Reclamo</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Gestión socioambiental de obra</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Transportes Rápidos del Sur S.A.S.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>6042223344</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Cl 40 Sur # 55-10</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>barrio 2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Material particulado y lodo en vía de acceso por flota de camiones del vecino industrial.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Juan Carlos Sanchez</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Edwin radica</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>patrullero 1</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Transportes Rápidos del Sur S.A.S.</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Autopista Sur Km 14 Bodega 8</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>6047778899</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>barrio 2</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Objetivo visita</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Situación encontrada</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Analisis de situacion</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>patrullero 1</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>456897</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>patrullero 1</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>establecimiento</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>132468732</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>cargo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6a2890f1a0cc341db</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-07 21:00:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-6</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Andres</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>calle sur envigado</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>barrio 1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>andres@gmail.com</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Queja / reporte ambiental</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Fauna doméstica</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>restaurante el puerquito</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>calle 1</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>barrio 1</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>maltratan perritos callejeros</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>respuesta</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Juan Carlos Sanchez</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Edwin radica</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6a288dd6df5510af0</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-09 22:02:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ENV-FLO-1-2026</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Jorge Iván Montoya</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>80123456</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Cl 38 Sur # 42-05</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3156677889</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>barrio 2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>jorge.montoya@email.com</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Telefono</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Sugerencia</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1034567890</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>3182233445</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Cl 39 Sur # 41-20</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>barrio 1</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Propuesta de siembra de árboles nativos en zona verde del barrio afectada por tala informal.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Juan Carlos Sanchez</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Edwin radica</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -64,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -75,8 +75,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV4"/>
+  <dimension ref="A1:AT8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -459,40 +457,38 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16.15" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14.45" customWidth="1" min="18" max="18"/>
-    <col width="27.2" customWidth="1" min="19" max="19"/>
-    <col width="22.1" customWidth="1" min="20" max="20"/>
-    <col width="21.25" customWidth="1" min="21" max="21"/>
-    <col width="22.1" customWidth="1" min="22" max="22"/>
-    <col width="19.55" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="16.15" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14.45" customWidth="1" min="17" max="17"/>
+    <col width="27.2" customWidth="1" min="18" max="18"/>
+    <col width="22.1" customWidth="1" min="19" max="19"/>
+    <col width="21.25" customWidth="1" min="20" max="20"/>
+    <col width="22.1" customWidth="1" min="21" max="21"/>
+    <col width="19.55" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
+    <col width="16.15" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="19.55" customWidth="1" min="28" max="28"/>
-    <col width="15.3" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="24.65" customWidth="1" min="31" max="31"/>
-    <col width="14.45" customWidth="1" min="32" max="32"/>
-    <col width="17" customWidth="1" min="33" max="33"/>
+    <col width="19.55" customWidth="1" min="27" max="27"/>
+    <col width="15.3" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="24.65" customWidth="1" min="30" max="30"/>
+    <col width="14.45" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
     <col width="14" customWidth="1" min="34" max="34"/>
     <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="16.15" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
-    <col width="20.4" customWidth="1" min="39" max="39"/>
+    <col width="16.15" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="37" max="37"/>
+    <col width="20.4" customWidth="1" min="38" max="38"/>
+    <col width="14" customWidth="1" min="39" max="39"/>
     <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="15.3" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14.45" customWidth="1" min="44" max="44"/>
-    <col width="18.7" customWidth="1" min="45" max="45"/>
-    <col width="17" customWidth="1" min="46" max="46"/>
-    <col width="17.85" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="15.3" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="14.45" customWidth="1" min="43" max="43"/>
+    <col width="18.7" customWidth="1" min="44" max="44"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="17.85" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -568,172 +564,162 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Categoría ambiental</t>
+          <t>Fecha de vencimiento</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de vencimiento</t>
+          <t>Última actuación</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Última actuación</t>
+          <t>Próxima actuación</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Próxima actuación</t>
+          <t>Perjudicante / posible afectante</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Perjudicante / posible afectante</t>
+          <t>Documento del perjudicante</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Documento del perjudicante</t>
+          <t>Teléfono del perjudicante</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Teléfono del perjudicante</t>
+          <t>Dirección del perjudicante</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Dirección del perjudicante</t>
+          <t>Barrio del perjudicante</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Barrio del perjudicante</t>
+          <t>Descripción de la queja / reporte</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Descripción de la queja / reporte</t>
+          <t>Respuesta inmediata</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Respuesta inmediata</t>
+          <t>Recibida por</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Recibida por</t>
+          <t>Remitido a</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Remitido a</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
           <t>Asignado a (patrullero)</t>
         </is>
       </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha de la visita</t>
+        </is>
+      </c>
       <c r="AC1" s="2" t="inlineStr">
         <is>
-          <t>Fecha de la visita</t>
+          <t>Fecha del acta</t>
         </is>
       </c>
       <c r="AD1" s="2" t="inlineStr">
         <is>
-          <t>Año acta</t>
+          <t>Autorización datos personales</t>
         </is>
       </c>
       <c r="AE1" s="2" t="inlineStr">
         <is>
-          <t>Autorización datos personales</t>
+          <t>Posible afectante</t>
         </is>
       </c>
       <c r="AF1" s="2" t="inlineStr">
         <is>
-          <t>Posible afectante</t>
+          <t>Dirección afectación</t>
         </is>
       </c>
       <c r="AG1" s="2" t="inlineStr">
         <is>
-          <t>Dirección afectación</t>
+          <t>Teléfono (acta)</t>
         </is>
       </c>
       <c r="AH1" s="2" t="inlineStr">
         <is>
-          <t>Teléfono (acta)</t>
+          <t>Barrio (acta)</t>
         </is>
       </c>
       <c r="AI1" s="2" t="inlineStr">
         <is>
-          <t>Barrio (acta)</t>
+          <t>Zona</t>
         </is>
       </c>
       <c r="AJ1" s="2" t="inlineStr">
         <is>
-          <t>Zona</t>
+          <t>Objeto de la visita</t>
         </is>
       </c>
       <c r="AK1" s="2" t="inlineStr">
         <is>
-          <t>Objeto de la visita</t>
+          <t>Situación encontrada</t>
         </is>
       </c>
       <c r="AL1" s="2" t="inlineStr">
         <is>
-          <t>Situación encontrada</t>
+          <t>Análisis de la situación</t>
         </is>
       </c>
       <c r="AM1" s="2" t="inlineStr">
         <is>
-          <t>Análisis de la situación</t>
+          <t>Conclusión</t>
         </is>
       </c>
       <c r="AN1" s="2" t="inlineStr">
         <is>
-          <t>Conclusión</t>
+          <t>Requerimientos</t>
         </is>
       </c>
       <c r="AO1" s="2" t="inlineStr">
         <is>
-          <t>Requerimientos</t>
+          <t>Nombre funcionario</t>
         </is>
       </c>
       <c r="AP1" s="2" t="inlineStr">
         <is>
-          <t>Nombre funcionario</t>
+          <t>C.C. funcionario</t>
         </is>
       </c>
       <c r="AQ1" s="2" t="inlineStr">
         <is>
-          <t>C.C. funcionario</t>
+          <t>Cargo funcionario</t>
         </is>
       </c>
       <c r="AR1" s="2" t="inlineStr">
         <is>
-          <t>Cargo funcionario</t>
+          <t>Nombre establecimiento</t>
         </is>
       </c>
       <c r="AS1" s="2" t="inlineStr">
         <is>
-          <t>Nombre establecimiento</t>
+          <t>C.C. establecimiento</t>
         </is>
       </c>
       <c r="AT1" s="2" t="inlineStr">
         <is>
-          <t>C.C. establecimiento</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
           <t>Cargo establecimiento</t>
-        </is>
-      </c>
-      <c r="AV1" s="4" t="inlineStr">
-        <is>
-          <t>Fecha del acta</t>
         </is>
       </c>
     </row>
@@ -810,172 +796,162 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>cCategoria</t>
+          <t>cFechaVencimiento</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>cFechaVencimiento</t>
+          <t>cUltimaActuacion</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>cUltimaActuacion</t>
+          <t>cProximaActuacion</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>cProximaActuacion</t>
+          <t>cPerjudicante</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>cPerjudicante</t>
+          <t>cDocumentoPerjudicante</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>cDocumentoPerjudicante</t>
+          <t>cTelefonoPerjudicante</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>cTelefonoPerjudicante</t>
+          <t>cDireccionPerjudicante</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>cDireccionPerjudicante</t>
+          <t>cBarrioPerjudicante</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>cBarrioPerjudicante</t>
+          <t>description</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>cRespuestaInmediata</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>cRespuestaInmediata</t>
+          <t>cRecibidaPor</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>cRecibidaPor</t>
+          <t>cRemitidoA</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
         <is>
-          <t>cRemitidoA</t>
+          <t>assignedUser</t>
         </is>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>assignedUser</t>
+          <t>fechaVisita</t>
         </is>
       </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>fechaVisita</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>anio</t>
+          <t>autorizacionDatos</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr">
         <is>
-          <t>autorizacionDatos</t>
+          <t>posibleAfectante</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr">
         <is>
-          <t>posibleAfectante</t>
+          <t>direccionAfectacion</t>
         </is>
       </c>
       <c r="AG2" s="3" t="inlineStr">
         <is>
-          <t>direccionAfectacion</t>
+          <t>telefono</t>
         </is>
       </c>
       <c r="AH2" s="3" t="inlineStr">
         <is>
-          <t>telefono</t>
+          <t>barrio</t>
         </is>
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>barrio</t>
+          <t>zona</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr">
         <is>
-          <t>zona</t>
+          <t>objetoVisita</t>
         </is>
       </c>
       <c r="AK2" s="3" t="inlineStr">
         <is>
-          <t>objetoVisita</t>
+          <t>situacionEncontrada</t>
         </is>
       </c>
       <c r="AL2" s="3" t="inlineStr">
         <is>
-          <t>situacionEncontrada</t>
+          <t>analisisSituacion</t>
         </is>
       </c>
       <c r="AM2" s="3" t="inlineStr">
         <is>
-          <t>analisisSituacion</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="AN2" s="3" t="inlineStr">
         <is>
-          <t>conclusion</t>
+          <t>requerimientos</t>
         </is>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
-          <t>requerimientos</t>
+          <t>funcionarioNombre</t>
         </is>
       </c>
       <c r="AP2" s="3" t="inlineStr">
         <is>
-          <t>funcionarioNombre</t>
+          <t>funcionarioCedula</t>
         </is>
       </c>
       <c r="AQ2" s="3" t="inlineStr">
         <is>
-          <t>funcionarioCedula</t>
+          <t>funcionarioCargo</t>
         </is>
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>funcionarioCargo</t>
+          <t>establecimientoNombre</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
         <is>
-          <t>establecimientoNombre</t>
+          <t>establecimientoCedula</t>
         </is>
       </c>
       <c r="AT2" s="3" t="inlineStr">
         <is>
-          <t>establecimientoCedula</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
           <t>establecimientoCargo</t>
-        </is>
-      </c>
-      <c r="AV2" s="5" t="inlineStr">
-        <is>
-          <t>fecha</t>
         </is>
       </c>
     </row>
@@ -1052,172 +1028,67 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Suelo</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>Remisión</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Remisión</t>
+          <t>Verificación</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Verificación</t>
+          <t>Constructora SAS</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Constructora SAS</t>
+          <t>3-5697</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3-5697</t>
+          <t>30256914</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>30256914</t>
+          <t>constructora@gmail.com</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>constructora@gmail.com</t>
+          <t>Alto de Misael</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Alto de Misael</t>
+          <t>Descripcion</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Descripcion</t>
+          <t>Respuesta</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Respuesta</t>
+          <t>Juan Carlos Sanchez</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Juan Carlos Sanchez</t>
+          <t>Edwin radica</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Edwin radica</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
           <t>patrullero 1</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Constructora SAS</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>calle 23 #40-09</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>3052661092</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Alto de Misael</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Urbano</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>objetivo visita</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>situacion encontrada</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>analisis de la situacion</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>conclusion</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>requerimientos</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>patrullero 1</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>12456</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>patrullero</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>establecimiento</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>128933</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>cargo</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -1292,63 +1163,681 @@
           <t>5</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>Remisión</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>lula martinez</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>lula martinez</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>El Chingui</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>respuesta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6a2a1c6fb67025f59</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:22:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ENV-LPR-1-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>industrias sas</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4-025698</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>calle 40</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>56987412</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Alto de Misael</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>industriasas@gmail.com</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ESPACIO PUBLICOS VERDES</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Afectaciones a la propiedad por arboles o vegetación</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Remisión</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Verificación</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>lula martinez</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>lula martinez</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>32189</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>El Chingui</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Marin Juarez</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>41165898731</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6354688</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Alto de Misael</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>respuesta</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Juan Carlos Sanchez</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Edwin radica</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6a2aef4e7c9a077a2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-11 17:17:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ENV-RSO-1-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Laura Gonzales</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4875962</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carrera 29 #20-16</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5220294</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Alto de Misael</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>laura@gmail.com</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>FLORA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Afectaciones asociadas a incendios o quemas</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>entidad 1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4-187549</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>587496321</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>carrera #32-8</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>El Chocho</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>patrullero 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6a2b16a6f2d6ad037</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-11 20:10:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Amalia Galindo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>487596</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>carrera 23</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>49856231</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>El Chocho</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>amaliaga@gmail.com</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>FAUNA SILVESTRE</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Presunto maltrato animal</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Braulio Goméz</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Braulio Goméz</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>487952</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>calle 23</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>El Chocho</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Maltrato animal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>llamar de inmediato policia ambiental y autoridades de bienestar animal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6a2b2520153839b66</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:11:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ENV-SUE-1-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Melisa Gutierrez</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10235964</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Calle 25</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7894</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>El Dorado</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>melisa@gmail.com</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>RESIDUOS SOLIDOS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Acumulación de escombros en el espacio publico</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ENTIDAD SAS</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1-987465</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>487596</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>calle 14</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>El Dorado</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Residuos solidos en las calles del barrio</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Respuesta inmediata</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>ENTIDAD SAS</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Calle 25</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>7894</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>El Dorado</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Urbano</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>objetivo visita</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>situación encontrada</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>analisis de situacion</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>conclusion</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>requerimientos</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>154689</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>patrullero</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>sector el dorado</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>784923</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>cargo</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT8"/>
+  <dimension ref="A1:AT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1193,7 +1193,6 @@
           <t>32189</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>El Chingui</t>
@@ -1219,7 +1218,6 @@
           <t>Edwin radica</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1838,6 +1836,263 @@
           <t>cargo</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6a3175f85c36a45a9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-16 16:11:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ENV-EPV-1-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>olga guzman</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5143556</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>carrera 10</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>56884213</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>El Chingui</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>olga@gmail.com</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ESPACIO PUBLICOS VERDES</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Afectación al ornato</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>cecilia urrego</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6843541354</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5876765</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>carrera 28</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>El Chingui</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>respuesta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6a2c824160aa2f48c</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-12 22:01:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Jorge lopez</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>546545</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>calle 34 número 10</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4544</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>El Chocho</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>jorge@gmail.com</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ESPACIO PUBLICOS VERDES</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Afectaciones por ruido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>insdustria textil</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1-4564645</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5454545</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>calle 25</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>El Chocho</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>mucho ruido</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>respuesta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT10"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1980,8 +1980,6 @@
           <t>2026-06-12 22:01:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Jorge lopez</t>
@@ -2092,7 +2090,131 @@
           <t>Edwin radica</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6a31bf1a71bb9fe07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-16 21:22:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Isabela Sánchez Ramírez</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>101756984</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>calle 23 #40-80</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3052661092</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bosques de Zúñiga</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>isabela@gmail.com</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>FLORA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Árbol en riesgo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Entidad SAS</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>56887563123</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5722028</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>carrera 55</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bosques de Zúñiga</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>respuesta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -1980,6 +1980,16 @@
           <t>2026-06-12 22:01:00</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ENV-HID-3-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-3</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Jorge lopez</t>
@@ -2017,7 +2027,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ESPACIO PUBLICOS VERDES</t>
+          <t>Hídrico</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2102,8 +2112,16 @@
           <t>2026-06-16 21:22:00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ENV-LPR-2-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-2</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Isabela Sánchez Ramírez</t>
@@ -2214,7 +2232,11 @@
           <t>Edwin radica</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>patrullero 2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT3"/>
+  <dimension ref="A1:AT7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1091,6 +1091,614 @@
           <t>patrullero 1</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Propiedad horizontal Edificio Los Robles</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Cra 42 # 18-45, apto 302</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>3005123456</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Las Flores</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Urbano</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>objetivo</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>situacion</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>conclusion</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>requerimientos</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>456987</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>patrullero</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>establecimientonombre</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>4134676</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>tal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6a31da428a0308813</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-16 23:18:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ENV-RSO-1-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Conjunto Residencial El Portal</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>900456789-1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cl 50 Sur # 42-10, admin conjunto</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6045551234</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>El Portal</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>admin@elportalconjunto.co</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>RESIDUOS SOLIDOS</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Disposición inadecuada de residuos sólidos en horas, dias y lugares no autorizados</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Respuesta DP u Oficio</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Clara Rodirguez</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>71234567</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3109876543</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Cl 50 Sur esquina Cra 42</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>El Portal</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>El local comercial saca bolsas de basura orgánica y escombros a la acera todos los días después de las 8 p.m. Genera mal olor, fauna y obstrucción del andén frente al conjunto.</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Queja recibida. Se remitirá a patrullero ambiental para constatar la situación en sitio.</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6a31db8c07f16bb80</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-16 23:23:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Carlos Andrés Mejía Ospina</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>43567890</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cra 48 # 25-12, casa 8</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3207654321</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Villagrande</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>carlos.mejia@email.com</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AIRE</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Afectaciones por ruido</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Visitas técnicos</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Constructora Horizonte S.A.S.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>890123456-7</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6048889900</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Obra en lote Cra 48 # 25-05</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Villagrande</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Obra en construcción opera martillos neumáticos y mezcladora desde las 5:30 a.m. de lunes a sábado. El ruido supera lo tolerable y afecta a varios vecinos del sector, incluidos menores de edad.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Se informó al peticionario que el caso será asignado para verificación de horarios y niveles de ruido.</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6a31dd8dc54daebc6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-16 23:30:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ana Lucía Vélez Montoya</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1019876543</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cl 65 # 48-22, int. 101</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3145567890</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>La Pradera</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ana.velez@email.com</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>HÍDRICO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Descarga inadecuada de aguas residuales o sin cumplimiento de requisitos</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fallo</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Lavandería Industrial San Jorge S.A.S.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>900234567-4</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6044456789</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Cl 65 # 48-10, bodega 2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>La Pradera</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Desde hace tres semanas el local vierte aguas grises con olor fuerte hacia la quebrada lateral. El líquido corre por la vía pública cuando llueve y afecta viviendas del sector.</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Queja registrada. Se programará visita de verificación para constatar la descarga y tomar muestras si aplica.</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6a31de28dda6f28db</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-16 23:35:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ENV-FDO-1-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Jorge Iván Duque Restrepo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>52897643</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cra 55 # 32-18 Teléfono</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3216789012</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>jorge.duke@email.com</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>FAUNA DOMÉSTICA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Presunto maltrato animal</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Informe técnico</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Audiencia</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Vecino propiedad Cra 55 # 32-14</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>80123456</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3001122334</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Cra 55 # 32-14</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Perros en el predio vecino permanecen amarrados todo el día sin agua ni sombra. Se escuchan aullidos frecuentes y el animal presenta signos de desnutrición visible desde la reja.</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Se recibió la denuncia. Se remitirá a patrullero ambiental para verificación in situ y actuación según protocolo de bienestar animal.</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>patrullero 2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -1746,7 +1746,6 @@
           <t>Las Flores</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Personal</t>
@@ -1797,7 +1796,6 @@
           <t>6045123456</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Zona Centro</t>
@@ -1826,6 +1824,101 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Restaurante El Fogón de Envigado</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Cra 48 # 32-15, apto 501</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>3109876543</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Las Flores</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Urbano</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>situacion</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>conclusion</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>requerimientos</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>patrullero</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>cargo</t>
         </is>
       </c>
     </row>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT8"/>
+  <dimension ref="A1:AT9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1922,6 +1922,229 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6a35829d865cb80ed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:53:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ENV-AIR-2-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Manuela Jimenez</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1245697</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>calle 24</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>312569470</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>El Dorado</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>manuelajimenez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AIRE</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Afectaciones por ruido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Oscar Galvis</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>665658</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>305269774</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>El Dorado</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>patrullero 2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Oscar Galvis</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>calle 24</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>312569470</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>El Dorado</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Urbano</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>situacion</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>conclusion</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>requerimientos</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>patrullero 2</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>123546</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>patrullero</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>establecimiento</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT9"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2149,465 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6a384d9d5dbee4ff4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ENV-HID-1-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Lucia Aristizabal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>89756423</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>calle 24</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>305261489</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Alcalá</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>HÍDRICO</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Descarga inadecuada de aguas residuales o sin cumplimiento de requisitos</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Constructora Gomez</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1-987456</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>36598741</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>cakke 24</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Alcalá</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Contaminacion de aguas</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>respuesta inmediata</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Constructora Gomez</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>calle 24</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>305261489</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Alcalá</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Urbano</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>xcbcfvf</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>hfhfdhf</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>fgfdgf</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>gfsdfgdgfd</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>gfdgfdgfd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>122465421</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>cargo</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>gdsgdfg</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>gfdgfdgdf</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>gfgfgfg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6a385b93c8bcad646</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-21 21:43:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ENV-FLO-2-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Martha Hernandez</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>102546987</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>calle 105</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>302698745</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>El Chocho</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>marthahernandez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>FLORA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Afectaciones a la propiedad por arboles o vegetación</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Hector Lopez</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10239564</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3052647</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>calle 105</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>El Chocho</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>dklskajdksandmnsa</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>adlksa;lkdlksajdkl</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Hector Lopez</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>calle 105</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>302698745</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>El Chocho</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Urbano</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>vdfgregytret</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>gffhfhcvc hfhf</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>fgfhfdyhtrutfghfh</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>tyfxfhgfhb</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>jtgnrngf,mnfmn,mn</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>565321321</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>dkfjfkdljfkdj</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>fdgdfgfg</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>321321</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>fghgfcvbv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT11"/>
+  <dimension ref="A1:AT12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2605,6 +2605,139 @@
       <c r="AT11" t="inlineStr">
         <is>
           <t>fghgfcvbv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6a398260c3412bf13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:40:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ENV-HID-2-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Jonathan Ochoa</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>102356987</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>calle 76</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>30265478</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>El Escobero</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>HÍDRICO</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Manejo inadecuado de aguas lluvias o escorrentia</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Empresas SAS</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>12356987</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>30265897</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>CALLE 78</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>El Escobero</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>respuesta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>patrullero 2</t>
         </is>
       </c>
     </row>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT12"/>
+  <dimension ref="A1:AT13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2654,7 +2654,6 @@
           <t>El Escobero</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Telefono</t>
@@ -2740,6 +2739,135 @@
           <t>patrullero 2</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6a39c1d77648b23a1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-22 23:12:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ENV-AIR-3-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>grftgregre</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>654353</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CL 9596 B Norte # 5435 B Norte - 574547 dfdfd fdfdz</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>54565564</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>El Escobero</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AIRE</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Acumulación de escombros en el espacio publico</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Archivado</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Audiencia</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>dcscdsc</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>85654</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>954341354</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>CL 656 G Norte # 46854 C Norte - 48454</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>El Escobero</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>fdfvds</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>fdsvfdvfd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -64,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -75,6 +75,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT13"/>
+  <dimension ref="A1:BU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,6 +491,33 @@
     <col width="18.7" customWidth="1" min="44" max="44"/>
     <col width="17" customWidth="1" min="45" max="45"/>
     <col width="17.85" customWidth="1" min="46" max="46"/>
+    <col width="22.1" customWidth="1" min="47" max="47"/>
+    <col width="23.8" customWidth="1" min="48" max="48"/>
+    <col width="26.35" customWidth="1" min="49" max="49"/>
+    <col width="20.4" customWidth="1" min="50" max="50"/>
+    <col width="23.8" customWidth="1" min="51" max="51"/>
+    <col width="21.25" customWidth="1" min="52" max="52"/>
+    <col width="26.35" customWidth="1" min="53" max="53"/>
+    <col width="28" customWidth="1" min="54" max="54"/>
+    <col width="17" customWidth="1" min="55" max="55"/>
+    <col width="17.85" customWidth="1" min="56" max="56"/>
+    <col width="19.55" customWidth="1" min="57" max="57"/>
+    <col width="22.1" customWidth="1" min="58" max="58"/>
+    <col width="21.25" customWidth="1" min="59" max="59"/>
+    <col width="19.55" customWidth="1" min="60" max="60"/>
+    <col width="15.3" customWidth="1" min="61" max="61"/>
+    <col width="14" customWidth="1" min="62" max="62"/>
+    <col width="14" customWidth="1" min="63" max="63"/>
+    <col width="21.25" customWidth="1" min="64" max="64"/>
+    <col width="23.8" customWidth="1" min="65" max="65"/>
+    <col width="17.85" customWidth="1" min="66" max="66"/>
+    <col width="21.25" customWidth="1" min="67" max="67"/>
+    <col width="18.7" customWidth="1" min="68" max="68"/>
+    <col width="23.8" customWidth="1" min="69" max="69"/>
+    <col width="27.2" customWidth="1" min="70" max="70"/>
+    <col width="14.45" customWidth="1" min="71" max="71"/>
+    <col width="15.3" customWidth="1" min="72" max="72"/>
+    <col width="17" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -722,6 +751,141 @@
           <t>Cargo establecimiento</t>
         </is>
       </c>
+      <c r="AU1" s="4" t="inlineStr">
+        <is>
+          <t>Documento del peticionario</t>
+        </is>
+      </c>
+      <c r="AV1" s="4" t="inlineStr">
+        <is>
+          <t>Vía principal (peticionario)</t>
+        </is>
+      </c>
+      <c r="AW1" s="4" t="inlineStr">
+        <is>
+          <t>N° vía principal (peticionario)</t>
+        </is>
+      </c>
+      <c r="AX1" s="4" t="inlineStr">
+        <is>
+          <t>Letra vía (peticionario)</t>
+        </is>
+      </c>
+      <c r="AY1" s="4" t="inlineStr">
+        <is>
+          <t>Cuadrante vía (peticionario)</t>
+        </is>
+      </c>
+      <c r="AZ1" s="4" t="inlineStr">
+        <is>
+          <t>Generadora (peticionario)</t>
+        </is>
+      </c>
+      <c r="BA1" s="4" t="inlineStr">
+        <is>
+          <t>Letra generadora (peticionario)</t>
+        </is>
+      </c>
+      <c r="BB1" s="4" t="inlineStr">
+        <is>
+          <t>Cuadrante generadora (peticionario)</t>
+        </is>
+      </c>
+      <c r="BC1" s="4" t="inlineStr">
+        <is>
+          <t>Placa (peticionario)</t>
+        </is>
+      </c>
+      <c r="BD1" s="4" t="inlineStr">
+        <is>
+          <t>Bloque (peticionario)</t>
+        </is>
+      </c>
+      <c r="BE1" s="4" t="inlineStr">
+        <is>
+          <t>Interior (peticionario)</t>
+        </is>
+      </c>
+      <c r="BF1" s="4" t="inlineStr">
+        <is>
+          <t>Dirección del peticionario</t>
+        </is>
+      </c>
+      <c r="BG1" s="4" t="inlineStr">
+        <is>
+          <t>Teléfono del peticionario</t>
+        </is>
+      </c>
+      <c r="BH1" s="4" t="inlineStr">
+        <is>
+          <t>Barrio del peticionario</t>
+        </is>
+      </c>
+      <c r="BI1" s="4" t="inlineStr">
+        <is>
+          <t>Correo electrónico</t>
+        </is>
+      </c>
+      <c r="BJ1" s="4" t="inlineStr">
+        <is>
+          <t>Canal de reporte</t>
+        </is>
+      </c>
+      <c r="BK1" s="4" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="BL1" s="4" t="inlineStr">
+        <is>
+          <t>Vía principal (infractor)</t>
+        </is>
+      </c>
+      <c r="BM1" s="4" t="inlineStr">
+        <is>
+          <t>N° vía principal (infractor)</t>
+        </is>
+      </c>
+      <c r="BN1" s="4" t="inlineStr">
+        <is>
+          <t>Letra vía (infractor)</t>
+        </is>
+      </c>
+      <c r="BO1" s="4" t="inlineStr">
+        <is>
+          <t>Cuadrante vía (infractor)</t>
+        </is>
+      </c>
+      <c r="BP1" s="4" t="inlineStr">
+        <is>
+          <t>Generadora (infractor)</t>
+        </is>
+      </c>
+      <c r="BQ1" s="4" t="inlineStr">
+        <is>
+          <t>Letra generadora (infractor)</t>
+        </is>
+      </c>
+      <c r="BR1" s="4" t="inlineStr">
+        <is>
+          <t>Cuadrante generadora (infractor)</t>
+        </is>
+      </c>
+      <c r="BS1" s="4" t="inlineStr">
+        <is>
+          <t>Placa (infractor)</t>
+        </is>
+      </c>
+      <c r="BT1" s="4" t="inlineStr">
+        <is>
+          <t>Bloque (infractor)</t>
+        </is>
+      </c>
+      <c r="BU1" s="4" t="inlineStr">
+        <is>
+          <t>Interior (infractor)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -954,6 +1118,141 @@
           <t>establecimientoCargo</t>
         </is>
       </c>
+      <c r="AU2" s="5" t="inlineStr">
+        <is>
+          <t>cDocumentoPeticionario</t>
+        </is>
+      </c>
+      <c r="AV2" s="5" t="inlineStr">
+        <is>
+          <t>cViaPrincipalPeticionario</t>
+        </is>
+      </c>
+      <c r="AW2" s="5" t="inlineStr">
+        <is>
+          <t>cNumViaPrincipalPeticionario</t>
+        </is>
+      </c>
+      <c r="AX2" s="5" t="inlineStr">
+        <is>
+          <t>cLetraViaPrincipalPeticionario</t>
+        </is>
+      </c>
+      <c r="AY2" s="5" t="inlineStr">
+        <is>
+          <t>cCuadranteViaPrincipalPeticionario</t>
+        </is>
+      </c>
+      <c r="AZ2" s="5" t="inlineStr">
+        <is>
+          <t>cGeneradoraPeticionario</t>
+        </is>
+      </c>
+      <c r="BA2" s="5" t="inlineStr">
+        <is>
+          <t>cLetraGeneradoraPeticionario</t>
+        </is>
+      </c>
+      <c r="BB2" s="5" t="inlineStr">
+        <is>
+          <t>cCuadranteGeneradoraPeticionario</t>
+        </is>
+      </c>
+      <c r="BC2" s="5" t="inlineStr">
+        <is>
+          <t>cPlacaPeticionario</t>
+        </is>
+      </c>
+      <c r="BD2" s="5" t="inlineStr">
+        <is>
+          <t>cBloquePeticionario</t>
+        </is>
+      </c>
+      <c r="BE2" s="5" t="inlineStr">
+        <is>
+          <t>cInteriorPeticionario</t>
+        </is>
+      </c>
+      <c r="BF2" s="5" t="inlineStr">
+        <is>
+          <t>cDireccionPeticionario</t>
+        </is>
+      </c>
+      <c r="BG2" s="5" t="inlineStr">
+        <is>
+          <t>cTelefonoPeticionario</t>
+        </is>
+      </c>
+      <c r="BH2" s="5" t="inlineStr">
+        <is>
+          <t>cBarrioPeticionario</t>
+        </is>
+      </c>
+      <c r="BI2" s="5" t="inlineStr">
+        <is>
+          <t>cCorreoPeticionario</t>
+        </is>
+      </c>
+      <c r="BJ2" s="5" t="inlineStr">
+        <is>
+          <t>cCanalDeReportePeticionario</t>
+        </is>
+      </c>
+      <c r="BK2" s="5" t="inlineStr">
+        <is>
+          <t>cZonaAlcaldiaPeticionario</t>
+        </is>
+      </c>
+      <c r="BL2" s="5" t="inlineStr">
+        <is>
+          <t>cViaPrincipalPerjudicante</t>
+        </is>
+      </c>
+      <c r="BM2" s="5" t="inlineStr">
+        <is>
+          <t>cNumViaPrincipalPerjudicante</t>
+        </is>
+      </c>
+      <c r="BN2" s="5" t="inlineStr">
+        <is>
+          <t>cLetraViaPrincipalPerjudicante</t>
+        </is>
+      </c>
+      <c r="BO2" s="5" t="inlineStr">
+        <is>
+          <t>cCuadranteViaPrincipalPerjudicante</t>
+        </is>
+      </c>
+      <c r="BP2" s="5" t="inlineStr">
+        <is>
+          <t>cGeneradoraPerjudicante</t>
+        </is>
+      </c>
+      <c r="BQ2" s="5" t="inlineStr">
+        <is>
+          <t>cLetraGeneradoraPerjudicante</t>
+        </is>
+      </c>
+      <c r="BR2" s="5" t="inlineStr">
+        <is>
+          <t>cCuadranteGeneradoraPerjudicante</t>
+        </is>
+      </c>
+      <c r="BS2" s="5" t="inlineStr">
+        <is>
+          <t>cPlacaPerjudicante</t>
+        </is>
+      </c>
+      <c r="BT2" s="5" t="inlineStr">
+        <is>
+          <t>cBloquePerjudicante</t>
+        </is>
+      </c>
+      <c r="BU2" s="5" t="inlineStr">
+        <is>
+          <t>cInteriorPerjudicante</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2786,7 +3085,6 @@
           <t>El Escobero</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Telefono</t>
@@ -2867,7 +3165,231 @@
           <t>Edwin radica</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6a3aaaded55f8315f</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-23 15:47:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>gredfgdgd</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ESPACIO PUBLICOS VERDES</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Afectaciones asociadas a incendios o quemas</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Orden de policía</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>fvdvfdgv dfdgf</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2435435435</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>32312</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>KR 6544654 F Este # 35354 B Norte - 6552 fgfdg fgdgfd</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>El Dorado</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>fgdgdf</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>ffgdfdgfdfd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>1353652</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>21332</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>53212321</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>6251321</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>dfgfg</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>gfg</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>KR 21332 B Este # 53212321 B Sur - 6251321 dfgfg gfg</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>6455645</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Bosques de Zuñiga</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>hgffdg@jgflkjgf.com</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>6544654</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>35354</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>6552</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>fgfdg</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>fgdgfd</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
